--- a/data/results/hr_logger_3hz_analysis.xlsx
+++ b/data/results/hr_logger_3hz_analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jehyu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_projects\Git\motion-aware-hr-monitor\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C205DD2-9625-42A7-AC9E-AE4A2E0D72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EE9692-BCC5-47BD-8421-C4C1E573BA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
   <si>
-    <t>sample_id</t>
-  </si>
-  <si>
     <t>hr_fft</t>
   </si>
   <si>
@@ -180,10 +177,13 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>This workbook was generated from the filtered 100-row CSV log.</t>
-  </si>
-  <si>
     <t>Computed error is final HR minus external reference HR; absolute error is used for MAE and max error.</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>This workbook was generated from the filtered 60-row CSV log.</t>
   </si>
 </sst>
 </file>
@@ -562,14 +562,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable_3Hz" displayName="DataTable_3Hz" ref="A1:Q61">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="sample_id"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="seconds"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="hr_fft"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="conf_fft"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="peak_hz"/>
@@ -764,60 +760,60 @@
   <sheetData>
     <row r="1" spans="1:17" ht="14.65" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="3">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>82.3</v>
@@ -841,7 +837,7 @@
         <v>0.73</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -872,7 +868,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="3">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>82.7</v>
@@ -896,7 +892,7 @@
         <v>0.69</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3">
         <v>0.04</v>
@@ -927,7 +923,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3">
-        <v>236</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>83.7</v>
@@ -951,7 +947,7 @@
         <v>0.68</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -982,7 +978,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3">
-        <v>237</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>85</v>
@@ -1006,7 +1002,7 @@
         <v>0.79</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3">
         <v>0.01</v>
@@ -1037,7 +1033,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="3">
-        <v>238</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>86.2</v>
@@ -1061,7 +1057,7 @@
         <v>0.51</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" s="3">
         <v>0.18</v>
@@ -1092,7 +1088,7 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="3">
-        <v>239</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>86.6</v>
@@ -1116,7 +1112,7 @@
         <v>0.33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" s="3">
         <v>0.18</v>
@@ -1147,7 +1143,7 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="3">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>86.6</v>
@@ -1171,7 +1167,7 @@
         <v>0.32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3">
         <v>0.13</v>
@@ -1202,7 +1198,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="3">
-        <v>241</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>87.3</v>
@@ -1226,7 +1222,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" s="3">
         <v>0.02</v>
@@ -1257,7 +1253,7 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="3">
-        <v>242</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>89.5</v>
@@ -1281,7 +1277,7 @@
         <v>0.7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3">
         <v>0.04</v>
@@ -1312,7 +1308,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3">
-        <v>243</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <v>91.5</v>
@@ -1336,7 +1332,7 @@
         <v>0.77</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -1367,7 +1363,7 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>92.8</v>
@@ -1391,7 +1387,7 @@
         <v>0.75</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="3">
         <v>0.02</v>
@@ -1422,7 +1418,7 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="3">
-        <v>245</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>93</v>
@@ -1446,7 +1442,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3">
         <v>0.12</v>
@@ -1477,7 +1473,7 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="3">
-        <v>246</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>91</v>
@@ -1501,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" s="3">
         <v>0.12</v>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3">
-        <v>247</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>0</v>
@@ -1556,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" s="3">
         <v>0.02</v>
@@ -1587,7 +1583,7 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="3">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>92.2</v>
@@ -1611,7 +1607,7 @@
         <v>0.49</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" s="3">
         <v>0.1</v>
@@ -1642,7 +1638,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="3">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>91.2</v>
@@ -1666,7 +1662,7 @@
         <v>0.62</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="3">
         <v>0.16</v>
@@ -1697,7 +1693,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="3">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>90.5</v>
@@ -1721,7 +1717,7 @@
         <v>0.7</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" s="3">
         <v>0.05</v>
@@ -1752,7 +1748,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="3">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>90.2</v>
@@ -1776,7 +1772,7 @@
         <v>0.8</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="3">
         <v>0.1</v>
@@ -1807,7 +1803,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="3">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
         <v>90.2</v>
@@ -1831,7 +1827,7 @@
         <v>0.62</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" s="3">
         <v>0.02</v>
@@ -1862,7 +1858,7 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="3">
-        <v>253</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
         <v>90.2</v>
@@ -1886,7 +1882,7 @@
         <v>0.63</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" s="3">
         <v>0.01</v>
@@ -1917,7 +1913,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="3">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3">
         <v>89.6</v>
@@ -1941,7 +1937,7 @@
         <v>0.63</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1972,7 +1968,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="3">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>89.2</v>
@@ -1996,7 +1992,7 @@
         <v>0.87</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" s="3">
         <v>0.09</v>
@@ -2027,7 +2023,7 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="3">
-        <v>256</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
         <v>89.1</v>
@@ -2051,7 +2047,7 @@
         <v>0.77</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" s="3">
         <v>0.06</v>
@@ -2082,7 +2078,7 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="3">
-        <v>257</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3">
         <v>88.9</v>
@@ -2106,7 +2102,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" s="3">
         <v>0.21</v>
@@ -2137,7 +2133,7 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="3">
-        <v>258</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3">
         <v>88.6</v>
@@ -2161,7 +2157,7 @@
         <v>0.34</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" s="3">
         <v>0.08</v>
@@ -2192,7 +2188,7 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="3">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3">
         <v>88.6</v>
@@ -2216,7 +2212,7 @@
         <v>0.36</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" s="3">
         <v>0.21</v>
@@ -2247,7 +2243,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="3">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3">
         <v>88.6</v>
@@ -2271,7 +2267,7 @@
         <v>0.39</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="3">
         <v>0.1</v>
@@ -2302,7 +2298,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="3">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3">
         <v>88.3</v>
@@ -2326,7 +2322,7 @@
         <v>0.59</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" s="3">
         <v>0.06</v>
@@ -2357,7 +2353,7 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="3">
-        <v>262</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3">
         <v>88.1</v>
@@ -2381,7 +2377,7 @@
         <v>0.6</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" s="3">
         <v>0.18</v>
@@ -2412,7 +2408,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="3">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3">
         <v>87.3</v>
@@ -2436,7 +2432,7 @@
         <v>0.78</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3">
         <v>7.0000000000000007E-2</v>
@@ -2467,7 +2463,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="3">
-        <v>264</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3">
         <v>86.1</v>
@@ -2491,7 +2487,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2522,7 +2518,7 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="3">
-        <v>265</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3">
         <v>86.5</v>
@@ -2546,7 +2542,7 @@
         <v>0.37</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" s="3">
         <v>0.11</v>
@@ -2577,7 +2573,7 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="3">
-        <v>266</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3">
         <v>86.5</v>
@@ -2601,7 +2597,7 @@
         <v>0.36</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34" s="3">
         <v>0.13</v>
@@ -2632,7 +2628,7 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="3">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="B35" s="3">
         <v>86.3</v>
@@ -2656,7 +2652,7 @@
         <v>0.49</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" s="3">
         <v>7.0000000000000007E-2</v>
@@ -2687,7 +2683,7 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="3">
-        <v>268</v>
+        <v>34</v>
       </c>
       <c r="B36" s="3">
         <v>86.5</v>
@@ -2711,7 +2707,7 @@
         <v>0.66</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" s="3">
         <v>0.13</v>
@@ -2742,7 +2738,7 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="3">
-        <v>269</v>
+        <v>35</v>
       </c>
       <c r="B37" s="3">
         <v>86.8</v>
@@ -2766,7 +2762,7 @@
         <v>0.64</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" s="3">
         <v>0</v>
@@ -2797,7 +2793,7 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="3">
-        <v>270</v>
+        <v>36</v>
       </c>
       <c r="B38" s="3">
         <v>86.8</v>
@@ -2821,7 +2817,7 @@
         <v>0.64</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3">
         <v>0.05</v>
@@ -2852,7 +2848,7 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="3">
-        <v>271</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3">
         <v>86</v>
@@ -2876,7 +2872,7 @@
         <v>0.68</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -2907,7 +2903,7 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="3">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3">
         <v>85.4</v>
@@ -2931,7 +2927,7 @@
         <v>0.68</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3">
         <v>0.04</v>
@@ -2962,7 +2958,7 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="3">
-        <v>273</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3">
         <v>85.6</v>
@@ -2986,7 +2982,7 @@
         <v>0.76</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41" s="3">
         <v>0.13</v>
@@ -3017,7 +3013,7 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="3">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3">
         <v>86.6</v>
@@ -3041,7 +3037,7 @@
         <v>0.49</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J42" s="3">
         <v>0.04</v>
@@ -3072,7 +3068,7 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="3">
-        <v>275</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3">
         <v>86.9</v>
@@ -3096,7 +3092,7 @@
         <v>0.34</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J43" s="3">
         <v>0.11</v>
@@ -3127,7 +3123,7 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="3">
-        <v>276</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3">
         <v>86.4</v>
@@ -3151,7 +3147,7 @@
         <v>0.49</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3182,7 +3178,7 @@
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="3">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3">
         <v>86.4</v>
@@ -3206,7 +3202,7 @@
         <v>0.54</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3237,7 +3233,7 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="3">
-        <v>278</v>
+        <v>44</v>
       </c>
       <c r="B46" s="3">
         <v>86.8</v>
@@ -3261,7 +3257,7 @@
         <v>0.35</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" s="3">
         <v>0.05</v>
@@ -3292,7 +3288,7 @@
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="3">
-        <v>279</v>
+        <v>45</v>
       </c>
       <c r="B47" s="3">
         <v>86.8</v>
@@ -3316,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J47" s="3">
         <v>0.11</v>
@@ -3347,7 +3343,7 @@
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="3">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -3371,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J48" s="3">
         <v>0.13</v>
@@ -3402,7 +3398,7 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="3">
-        <v>281</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3">
         <v>86.8</v>
@@ -3426,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J49" s="3">
         <v>0.21</v>
@@ -3457,7 +3453,7 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="3">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="B50" s="3">
         <v>86.8</v>
@@ -3481,7 +3477,7 @@
         <v>0.35</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" s="3">
         <v>0.23</v>
@@ -3512,7 +3508,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="3">
-        <v>283</v>
+        <v>49</v>
       </c>
       <c r="B51" s="3">
         <v>85.8</v>
@@ -3536,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J51" s="3">
         <v>0.19</v>
@@ -3567,7 +3563,7 @@
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="3">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="B52" s="3">
         <v>84.9</v>
@@ -3591,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J52" s="3">
         <v>0.17</v>
@@ -3622,7 +3618,7 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="3">
-        <v>285</v>
+        <v>51</v>
       </c>
       <c r="B53" s="3">
         <v>85.6</v>
@@ -3646,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J53" s="3">
         <v>0.17</v>
@@ -3677,7 +3673,7 @@
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="3">
-        <v>286</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3">
         <v>85.8</v>
@@ -3701,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J54" s="3">
         <v>0.12</v>
@@ -3732,7 +3728,7 @@
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="3">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3">
         <v>86.3</v>
@@ -3756,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J55" s="3">
         <v>0.01</v>
@@ -3787,7 +3783,7 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="3">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="B56" s="3">
         <v>86.6</v>
@@ -3811,7 +3807,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -3842,7 +3838,7 @@
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="3">
-        <v>289</v>
+        <v>55</v>
       </c>
       <c r="B57" s="3">
         <v>86.3</v>
@@ -3866,7 +3862,7 @@
         <v>0.7</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3897,7 +3893,7 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="3">
-        <v>290</v>
+        <v>56</v>
       </c>
       <c r="B58" s="3">
         <v>85.7</v>
@@ -3921,7 +3917,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J58" s="3">
         <v>0.06</v>
@@ -3952,7 +3948,7 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="3">
-        <v>291</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3">
         <v>85.1</v>
@@ -3976,7 +3972,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" s="3">
         <v>0.02</v>
@@ -4007,7 +4003,7 @@
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="3">
-        <v>292</v>
+        <v>58</v>
       </c>
       <c r="B60" s="3">
         <v>85</v>
@@ -4031,7 +4027,7 @@
         <v>0.49</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" s="3">
         <v>0.03</v>
@@ -4062,7 +4058,7 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="3">
-        <v>293</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3">
         <v>0</v>
@@ -4086,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J61" s="3">
         <v>0.15</v>
@@ -4136,7 +4132,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4144,40 +4140,40 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="13">
         <f>COUNT(Data!G2:G61)</f>
         <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
       </c>
       <c r="G4">
         <f>B5</f>
@@ -4186,20 +4182,20 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="13">
         <f>AVERAGE(Data!Q2:Q61)</f>
         <v>1.1933333333333329</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="F5" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
       </c>
       <c r="G5">
         <f>B6</f>
@@ -4208,20 +4204,20 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="13">
         <f>SQRT(SUMSQ(Data!P2:P61)/COUNT(Data!P2:P61))</f>
         <v>1.4110279940525638</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>33</v>
       </c>
       <c r="G6">
         <f>B7</f>
@@ -4230,102 +4226,102 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="13">
         <f>MAX(Data!Q2:Q61)</f>
         <v>3.2000000000000028</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="13">
         <f>STDEV(Data!G2:G61)</f>
         <v>2.4398782038695113</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="15">
         <f>COUNTIF(Data!I2:I61,"HOLD")/COUNTA(Data!I2:I61)</f>
         <v>0.18333333333333332</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="13">
         <f>AVERAGE(Data!H2:H61)</f>
         <v>0.47333333333333333</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="13">
         <f>AVERAGE(Data!O2:O61)</f>
         <v>87.1</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="14">
         <f>AVERAGE(Data!G2:G61)</f>
         <v>87.523333333333326</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4333,7 +4329,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
